--- a/debug/judgements_intro/excel_overviews/gpt-4.1_vs_Llama-2-7b-chat-hf/Qwen3-Next-80B-A3B-Instruct/default/total_votes_file.xlsx
+++ b/debug/judgements_intro/excel_overviews/gpt-4.1_vs_Llama-2-7b-chat-hf/Qwen3-Next-80B-A3B-Instruct/default/total_votes_file.xlsx
@@ -430,13 +430,13 @@
         <v>7</v>
       </c>
       <c r="C2">
-        <v>400</v>
+        <v>398</v>
       </c>
       <c r="D2">
-        <v>17</v>
+        <v>18</v>
       </c>
       <c r="E2">
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="G2">
         <v>9</v>
@@ -450,7 +450,7 @@
         <v>8</v>
       </c>
       <c r="C3">
-        <v>408</v>
+        <v>407</v>
       </c>
       <c r="D3">
         <v>16</v>
@@ -459,7 +459,7 @@
         <v>1</v>
       </c>
       <c r="G3">
-        <v>1</v>
+        <v>2</v>
       </c>
       <c r="H3">
         <v>426</v>
